--- a/READING/6_19_12.xlsx
+++ b/READING/6_19_12.xlsx
@@ -466,37 +466,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>立派な</t>
+          <t>何より</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>出色的，宏伟的</t>
+          <t>比什么都...</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>りっぱな</t>
+          <t>なにより</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>〜は〜といわれる</t>
+          <t>どういう</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>...被称为...</t>
+          <t>什么样的，怎样的</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -504,24 +504,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>すべての</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>所有的</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>“あらゆる”全部，所有</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -542,7 +538,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -567,36 +563,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>あせって</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>着急地</t>
+          <t>仔细地，慢慢地</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>“ゆっくり”慢慢地</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ても仕方がない</t>
+          <t>あせって</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>...也没办法</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>てもしかたがない</t>
-        </is>
-      </c>
+          <t>着急地</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -605,33 +601,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>もち</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
+          <t>持ち</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>“ゆっくり”慢慢地</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>なさる</t>
+          <t>おのずとに</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“する”的尊敬语，上对下的语气</t>
+          <t>自然而然地</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -639,37 +631,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>何より</t>
+          <t>ふくらむ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>比什么都...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>なにより</t>
-        </is>
-      </c>
+          <t>膨胀；鼓起；扩大</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>もち</t>
+          <t>～ております</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>持ち</t>
+          <t>“ている”的自谦</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -677,16 +665,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>おのずとに</t>
+          <t>ようとして</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>自然而然地</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -698,24 +686,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>次第</t>
+          <t>ても仕方がない</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>取决于</t>
+          <t>...也没办法</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>しだい</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>“N/Ｖ＋次第”一…就...</t>
-        </is>
-      </c>
+          <t>てもしかたがない</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -723,33 +707,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>〜うち</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ぶしょ</t>
-        </is>
-      </c>
+          <t>在...期间；趁着</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>あとは</t>
+          <t>ともに</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>…之后</t>
+          <t>一起，同时</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -757,20 +737,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>～ております</t>
+          <t>すべての</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>“ている”的自谦</t>
+          <t>所有的</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>“あらゆる”全部，所有</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -778,33 +762,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>何かあったときに</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>发生什么事的时候</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>なにかあったときに</t>
+          <t>ぶしょ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ようとして</t>
+          <t>あとは</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>…之后</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -816,32 +800,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>どういう</t>
+          <t>出来る</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>什么样的，怎样的</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>能，会，可以</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>できる</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>何かあったときに</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>发生什么事的时候</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>なにかあったときに</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -884,7 +876,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -901,20 +893,28 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ふくらむ</t>
+          <t>次第</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>膨胀；鼓起；扩大</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>取决于</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>しだい</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>“N/Ｖ＋次第”一…就...</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -922,37 +922,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ともに</t>
+          <t>回り道</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>一起，同时</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>绕道，走弯路</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>まわりみち</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>あるいは</t>
+          <t>考え方がある</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>或者，也许</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>“〜または”或者</t>
-        </is>
-      </c>
+          <t>有...样的想法/看法</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>かんがえかたがある</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -960,40 +964,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>出来る</t>
+          <t>なさる</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>能，会，可以</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>できる</t>
-        </is>
-      </c>
+          <t>“する”的尊敬语，上对下的语气</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>任せる</t>
+          <t>といわれる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>委托，托付</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>まかせる</t>
-        </is>
-      </c>
+          <t>被称为...</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1002,76 +998,76 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>〜たり</t>
+          <t>立派な</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>...啦...啦（列举动作）</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>出色的，宏伟的</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>りっぱな</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>遅い</t>
+          <t>ともいえます</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>慢；迟；晚</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>おそい</t>
-        </is>
-      </c>
+          <t>也可以说是...</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>その一つ</t>
+          <t>不具合</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>其中之一</t>
+          <t>(机器)故障，(情况)不方便</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>そのひとつ</t>
+          <t>ふぐあい</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>的確に</t>
+          <t>約束</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>准确地，恰当地</t>
+          <t>约定，承诺</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>てきかくに</t>
+          <t>やくそく</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1082,17 +1078,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>考え方がある</t>
+          <t>〜に対して</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>有...样的想法/看法</t>
+          <t>对于…</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>かんがえかたがある</t>
+          <t>〜にたいして</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1103,113 +1099,109 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>目が行く</t>
+          <t>納品</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>注意到，目光投向</t>
+          <t>交货，送货</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>めがいく</t>
+          <t>のうひん</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>繰り返し</t>
+          <t>目が行く</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>重复，反复</t>
+          <t>注意到，目光投向</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>くりかえし</t>
+          <t>めがいく</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>思い込み</t>
+          <t>〜は〜といわれる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>深信，固执地认为</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>おもいこみ</t>
-        </is>
-      </c>
+          <t>...被称为...</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ミス</t>
+          <t>お手数ですが</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>失误，错误</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>虽然很麻烦</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>おてすうですが</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>〜に関する</t>
+          <t>〜により</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>关于...</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>〜にかんする</t>
-        </is>
-      </c>
+          <t>通过…</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>お知らせ</t>
+          <t>〜たり</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>通知</t>
+          <t>...啦...啦（列举动作）</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1217,37 +1209,33 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>不具合</t>
+          <t>だれだって</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(机器)故障，(情况)不方便</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ふぐあい</t>
-        </is>
-      </c>
+          <t>无论是谁都</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜だと</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>…的话</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1259,12 +1247,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>お知らせ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
+          <t>通知</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1293,19 +1281,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>〜を身につける</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>掌握...，学会...</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>〜をみにつける</t>
-        </is>
-      </c>
+          <t>所有的，一切的</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1314,37 +1298,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>順番</t>
+          <t>〜だと</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>顺序；次序</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>じゅんばん</t>
-        </is>
-      </c>
+          <t>…的话</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>〜において</t>
+          <t>あるいは</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>在…(方面，地点，时候)</t>
+          <t>或者，也许</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>“〜または”或者</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1352,12 +1336,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>スムーズに</t>
+          <t>ミス</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>顺利地</t>
+          <t>失误，错误</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1369,15 +1353,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>だから</t>
+          <t>〜に関する</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>所以，因此</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>关于...</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>〜にかんする</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1386,17 +1374,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>決して〜ない</t>
+          <t>順番</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>决不...</t>
+          <t>顺序；次序</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>けっして〜ない</t>
+          <t>じゅんばん</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1407,36 +1395,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>約束</t>
+          <t>思い込み</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>约定，承诺</t>
+          <t>深信，固执地认为</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>やくそく</t>
+          <t>おもいこみ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>だけ〜ばいい</t>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>只要...就行</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>重复，反复</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>くりかえし</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1445,59 +1437,59 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>〜に従って</t>
+          <t>任せる</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>遵照...，随着...</t>
+          <t>委托，托付</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>まかせる</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>〜に対して</t>
+          <t>〜を身につける</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>对于…</t>
+          <t>掌握...，学会...</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>〜にたいして</t>
+          <t>〜をみにつける</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>納品</t>
+          <t>決して〜ない</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>交货，送货</t>
+          <t>决不...</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>のうひん</t>
+          <t>けっして〜ない</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1508,33 +1500,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>〜が生じ</t>
+          <t>〜において</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>发生...</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>〜がしょうじ</t>
-        </is>
-      </c>
+          <t>在…(方面，地点，时候)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>〜により</t>
+          <t>スムーズに</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>通过…</t>
+          <t>顺利地</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1546,15 +1534,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>〜とらえる</t>
+          <t>話を広げる</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>视为...，理解为...</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>展开话题</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>はなしをひろげる</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -1563,19 +1555,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>合わせる</t>
+          <t>だけ〜ばいい</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>配合；合计</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>あわせる</t>
-        </is>
-      </c>
+          <t>只要...就行</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -1584,50 +1572,54 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>たとえ〜でも</t>
+          <t>〜に従って</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>即使...也...</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>遵照...，随着...</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>〜にしたがって</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>お手数ですが</t>
+          <t>〜が生じ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>虽然很麻烦</t>
+          <t>发生...</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>おてすうですが</t>
+          <t>〜がしょうじ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>だれだって</t>
+          <t>〜とらえる</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>无论是谁都</t>
+          <t>视为...，理解为...</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1639,17 +1631,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>下記の</t>
+          <t>合わせる</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>下述的，如下</t>
+          <t>配合；合计</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>かきの</t>
+          <t>あわせる</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1660,12 +1652,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>いつか</t>
+          <t>たとえ〜でも</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>总有一天，某个时间</t>
+          <t>即使...也...</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1677,17 +1669,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>それ以上に</t>
+          <t>下記の</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>在那之上，比那更...</t>
+          <t>下述的，如下</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>それいじょうに</t>
+          <t>かきの</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1698,36 +1690,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>話を広げる</t>
+          <t>その一つ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>展开话题</t>
+          <t>其中之一</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>はなしをひろげる</t>
+          <t>そのひとつ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>それ以上に</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>相当，非常</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>在那之上，比那更...</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>それいじょうに</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -1736,34 +1732,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>わけです</t>
+          <t>的確に</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>下结论</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>准确地，恰当地</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>てきかくに</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>必死に</t>
+          <t>妨げる</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>拼命地</t>
+          <t>妨碍，阻碍</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ひっしに</t>
+          <t>さまたげる</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>うまい</t>
+          <t>わけです</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>好吃的；高明的</t>
+          <t>下结论</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>〜なんか</t>
+          <t>やめる</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>...之类的（表轻视）</t>
+          <t>停止，放弃</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1808,17 +1808,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>強い</t>
+          <t>一方的に</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>强壮的，强烈的</t>
+          <t>单方面地</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>つよい</t>
+          <t>いっぽうてきに</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -1829,29 +1829,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>あえて</t>
+          <t>気味</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>敢于，硬要</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>有点...，感觉...</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>きみ</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ともいえます</t>
+          <t>うまい</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>也可以说是...</t>
+          <t>好吃的；高明的</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1859,16 +1863,16 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>といわれる</t>
+          <t>〜なんか</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>被称为...</t>
+          <t>...之类的（表轻视）</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1880,17 +1884,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>世話</t>
+          <t>強い</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>照顾，关照</t>
+          <t>强壮的，强烈的</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>せわ</t>
+          <t>つよい</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -1901,44 +1905,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>自慢する</t>
+          <t>あえて</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>自夸，炫耀</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>じまんする</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>“我慢”忍耐</t>
-        </is>
-      </c>
+          <t>敢于，硬要</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>外れ者</t>
+          <t>まだ～ない</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>被排挤的人，不合群的人</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>はずれもの</t>
-        </is>
-      </c>
+          <t>还没有…</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -1947,19 +1939,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>気になる</t>
+          <t>いっこうに〜ない</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>在意，担心</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>きになる</t>
-        </is>
-      </c>
+          <t>一点也(不)...</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -1968,38 +1956,38 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>次が</t>
+          <t>世話</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>下一个是...</t>
+          <t>照顾，关照</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>つぎが</t>
+          <t>せわ</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>回り道</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>绕道，走弯路</t>
+          <t>未必，不一定</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>まわりみち</t>
+          <t>とはかぎらない</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2010,37 +1998,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>見つかる</t>
+          <t>自慢する</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>被找到</t>
+          <t>自夸，炫耀</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>みつかる</t>
+          <t>じまんする</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>“みつける”寻找</t>
+          <t>“我慢”忍耐</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>まったく〜ない</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>马上，立刻</t>
+          <t>完全(不)...</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2052,12 +2040,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>たとえ</t>
+          <t>いつか</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>举例</t>
+          <t>总有一天，某个时间</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2069,15 +2057,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>たしかに</t>
+          <t>外れ者</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>的确，确实</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>被排挤的人，不合群的人</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>はずれもの</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -2086,17 +2078,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>気味</t>
+          <t>気になる</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>有点...，感觉...</t>
+          <t>在意，担心</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>きみ</t>
+          <t>きになる</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2107,19 +2099,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>一方的に</t>
+          <t>なぜなら</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>单方面地</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>いっぽうてきに</t>
-        </is>
-      </c>
+          <t>要说为什么…</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -2128,15 +2116,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>のに</t>
+          <t>次が</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>为了…；转折</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>下一个是...</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>つぎが</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -2145,15 +2137,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>なぜなら</t>
+          <t>必死に</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>要说为什么…</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>拼命地</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ひっしに</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -2162,12 +2158,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>まったく〜ない</t>
+          <t>のに</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>完全(不)...</t>
+          <t>为了…；转折</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2179,16 +2175,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>やめる</t>
+          <t>見つかる</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>停止，放弃</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+          <t>被找到</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>みつかる</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>“みつける”寻找</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2196,19 +2200,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>すぐに</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>とはかぎらない</t>
-        </is>
-      </c>
+          <t>马上，立刻</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>いっこうに〜ない</t>
+          <t>たとえ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>一点也(不)...</t>
+          <t>举例</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>まだ～ない</t>
+          <t>たしかに</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>还没有…</t>
+          <t>的确，确实</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2251,17 +2251,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>妨げる</t>
+          <t>遅い</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>妨碍，阻碍</t>
+          <t>慢；迟；晚</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>さまたげる</t>
+          <t>おそい</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>〜うち</t>
+          <t>だから</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>在...期间；趁着</t>
+          <t>所以，因此</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>

--- a/READING/6_19_12.xlsx
+++ b/READING/6_19_12.xlsx
@@ -466,37 +466,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>何より</t>
+          <t>あせって</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>比什么都...</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>なにより</t>
-        </is>
-      </c>
+          <t>着急地</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>どういう</t>
+          <t>ふくらむ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>什么样的，怎样的</t>
+          <t>膨胀；鼓起；扩大</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -504,16 +500,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>おのずとに</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>自然而然地</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -521,16 +517,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>どのように</t>
+          <t>～ております</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>以…方式</t>
+          <t>“ている”的自谦</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -538,58 +534,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>お手数ですが</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
+          <t>虽然很麻烦</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>とはかぎらない</t>
+          <t>おてすうですが</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>ようとして</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>“ゆっくり”慢慢地</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>あせって</t>
+          <t>〜により</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>着急地</t>
+          <t>通过…</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -597,16 +589,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>もち</t>
+          <t>どういう</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>持ち</t>
+          <t>什么样的，怎样的</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -618,15 +610,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>おのずとに</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>自然而然地</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>未必，不一定</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>とはかぎらない</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -635,12 +631,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ふくらむ</t>
+          <t>もち</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>膨胀；鼓起；扩大</t>
+          <t>持ち</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -648,19 +644,23 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>～ております</t>
+          <t>出来る</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>“ている”的自谦</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>能，会，可以</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>できる</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -669,12 +669,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ようとして</t>
+          <t>ともいえます</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>也可以说是...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -682,37 +682,33 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ても仕方がない</t>
+          <t>〜も〜ば〜も</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>...也没办法</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>てもしかたがない</t>
-        </is>
-      </c>
+          <t>既...又...</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>〜うち</t>
+          <t>だれだって</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>在...期间；趁着</t>
+          <t>无论是谁都</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -720,79 +716,83 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ともに</t>
+          <t>何より</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>一起，同时</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>比什么都...</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>なにより</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>すべての</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>所有的</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>“あらゆる”全部，所有</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ぶしょ</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>仔细地，慢慢地</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>“ゆっくり”慢慢地</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>あとは</t>
+          <t>あるいは</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>…之后</t>
+          <t>或者，也许</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>“〜または”或者</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -800,54 +800,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>出来る</t>
+          <t>どのように</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>能，会，可以</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>できる</t>
-        </is>
-      </c>
+          <t>以…方式</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>何かあったときに</t>
+          <t>〜は〜といわれる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>发生什么事的时候</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>なにかあったときに</t>
-        </is>
-      </c>
+          <t>...被称为...</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>だろうか</t>
+          <t>といわれる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(1)反问，是…吗？(2)推测</t>
+          <t>被称为...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -855,23 +847,19 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>話し出し</t>
+          <t>ともに</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>开口说话，开场白</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>はなしだし</t>
-        </is>
-      </c>
+          <t>一起，同时</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -880,15 +868,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>〜も〜ば〜も</t>
+          <t>目が行く</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>既...又...</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>注意到，目光投向</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>めがいく</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -897,24 +889,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>次第</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>取决于</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>しだい</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>“N/Ｖ＋次第”一…就...</t>
-        </is>
-      </c>
+          <t>ぶしょ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -922,17 +910,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>回り道</t>
+          <t>納品</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>绕道，走弯路</t>
+          <t>交货，送货</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>まわりみち</t>
+          <t>のうひん</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -943,33 +931,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>考え方がある</t>
+          <t>まったく〜ない</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>有...样的想法/看法</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>かんがえかたがある</t>
-        </is>
-      </c>
+          <t>完全(不)...</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>なさる</t>
+          <t>まだ～ない</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>“する”的尊敬语，上对下的语气</t>
+          <t>还没有…</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -977,19 +961,23 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>といわれる</t>
+          <t>妨げる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>被称为...</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>妨碍，阻碍</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>さまたげる</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -998,19 +986,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>立派な</t>
+          <t>〜たり</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>出色的，宏伟的</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>りっぱな</t>
-        </is>
-      </c>
+          <t>...啦...啦（列举动作）</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1019,15 +1003,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ともいえます</t>
+          <t>思い込み</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>也可以说是...</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>深信，固执地认为</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>おもいこみ</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1036,19 +1024,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>不具合</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(机器)故障，(情况)不方便</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ふぐあい</t>
-        </is>
-      </c>
+          <t>相当，非常</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1057,17 +1041,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>約束</t>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>约定，承诺</t>
+          <t>重复，反复</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>やくそく</t>
+          <t>くりかえし</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1078,17 +1062,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>〜に対して</t>
+          <t>約束</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>对于…</t>
+          <t>约定，承诺</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>〜にたいして</t>
+          <t>やくそく</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1099,54 +1083,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>納品</t>
+          <t>〜に対して</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>交货，送货</t>
+          <t>对于…</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>のうひん</t>
+          <t>〜にたいして</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>目が行く</t>
+          <t>〜うち</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>注意到，目光投向</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>めがいく</t>
-        </is>
-      </c>
+          <t>在...期间；趁着</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜は〜といわれる</t>
+          <t>だから</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>...被称为...</t>
+          <t>所以，因此</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1154,41 +1134,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>お手数ですが</t>
+          <t>何かあったときに</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>虽然很麻烦</t>
+          <t>发生什么事的时候</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>おてすうですが</t>
+          <t>なにかあったときに</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>〜により</t>
+          <t>すべての</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>通过…</t>
+          <t>所有的</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>“あらゆる”全部，所有</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1196,12 +1180,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>〜たり</t>
+          <t>あとは</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>...啦...啦（列举动作）</t>
+          <t>…之后</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1209,19 +1193,23 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>だれだって</t>
+          <t>不具合</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>无论是谁都</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>(机器)故障，(情况)不方便</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ふぐあい</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1230,12 +1218,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>だろうか</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>相当，非常</t>
+          <t>(1)反问，是…吗？(2)推测</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1243,71 +1231,91 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>お知らせ</t>
+          <t>ても仕方がない</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>...也没办法</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>てもしかたがない</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>である</t>
+          <t>話し出し</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>是...（です的书面语）</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>开口说话，开场白</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>はなしだし</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>立派な</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>出色的，宏伟的</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>りっぱな</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜だと</t>
+          <t>次第</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>…的话</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>取决于</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>しだい</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>“N/Ｖ＋次第”一…就...</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1315,57 +1323,57 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>あるいは</t>
+          <t>回り道</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>或者，也许</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>“〜または”或者</t>
-        </is>
-      </c>
+          <t>绕道，走弯路</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>まわりみち</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ミス</t>
+          <t>考え方がある</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>失误，错误</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>有...样的想法/看法</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>かんがえかたがある</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>〜に関する</t>
+          <t>なさる</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>关于...</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>〜にかんする</t>
-        </is>
-      </c>
+          <t>“する”的尊敬语，上对下的语气</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1374,59 +1382,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>順番</t>
+          <t>必死に</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>顺序；次序</t>
+          <t>拼命地</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>じゅんばん</t>
+          <t>ひっしに</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>思い込み</t>
+          <t>いつか</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>深信，固执地认为</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>おもいこみ</t>
-        </is>
-      </c>
+          <t>总有一天，某个时间</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>繰り返し</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>重复，反复</t>
+          <t>未必，不一定</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>くりかえし</t>
+          <t>とはかぎらない</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1437,17 +1441,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>任せる</t>
+          <t>世話</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>委托，托付</t>
+          <t>照顾，关照</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>まかせる</t>
+          <t>せわ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1458,19 +1462,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>〜を身につける</t>
+          <t>いっこうに〜ない</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>掌握...，学会...</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>〜をみにつける</t>
-        </is>
-      </c>
+          <t>一点也(不)...</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -1479,17 +1479,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>決して〜ない</t>
+          <t>強い</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>决不...</t>
+          <t>强壮的，强烈的</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>けっして〜ない</t>
+          <t>つよい</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>〜において</t>
+          <t>あえて</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>在…(方面，地点，时候)</t>
+          <t>敢于，硬要</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>スムーズに</t>
+          <t>〜なんか</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>顺利地</t>
+          <t>...之类的（表轻视）</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1534,19 +1534,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>話を広げる</t>
+          <t>うまい</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>展开话题</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>はなしをひろげる</t>
-        </is>
-      </c>
+          <t>好吃的；高明的</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -1555,16 +1551,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>だけ〜ばいい</t>
+          <t>自慢する</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>只要...就行</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+          <t>自夸，炫耀</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>じまんする</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>“我慢”忍耐</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1572,17 +1576,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>〜に従って</t>
+          <t>一方的に</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>遵照...，随着...</t>
+          <t>单方面地</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>いっぽうてきに</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -1593,17 +1597,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>〜が生じ</t>
+          <t>外れ者</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>发生...</t>
+          <t>被排挤的人，不合群的人</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>〜がしょうじ</t>
+          <t>はずれもの</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -1614,15 +1618,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>〜とらえる</t>
+          <t>気味</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>视为...，理解为...</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>有点...，感觉...</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>きみ</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -1631,17 +1639,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>合わせる</t>
+          <t>気になる</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>配合；合计</t>
+          <t>在意，担心</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>あわせる</t>
+          <t>きになる</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1652,12 +1660,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>たとえ〜でも</t>
+          <t>なぜなら</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>即使...也...</t>
+          <t>要说为什么…</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1669,17 +1677,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>下記の</t>
+          <t>次が</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>下述的，如下</t>
+          <t>下一个是...</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>かきの</t>
+          <t>つぎが</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1690,19 +1698,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>その一つ</t>
+          <t>すぐに</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>其中之一</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>そのひとつ</t>
-        </is>
-      </c>
+          <t>马上，立刻</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -1711,19 +1715,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>それ以上に</t>
+          <t>のに</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>在那之上，比那更...</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>それいじょうに</t>
-        </is>
-      </c>
+          <t>为了…；转折</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -1732,40 +1732,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>的確に</t>
+          <t>見つかる</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>准确地，恰当地</t>
+          <t>被找到</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>てきかくに</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>みつかる</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>“みつける”寻找</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>妨げる</t>
+          <t>たとえ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>妨碍，阻碍</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>さまたげる</t>
-        </is>
-      </c>
+          <t>举例</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>わけです</t>
+          <t>たしかに</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>下结论</t>
+          <t>的确，确实</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1791,15 +1791,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>やめる</t>
+          <t>遅い</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>停止，放弃</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>慢；迟；晚</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>おそい</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -1808,17 +1812,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>一方的に</t>
+          <t>その一つ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>单方面地</t>
+          <t>其中之一</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>いっぽうてきに</t>
+          <t>そのひとつ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -1829,17 +1833,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>気味</t>
+          <t>合わせる</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>有点...，感觉...</t>
+          <t>配合；合计</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>きみ</t>
+          <t>あわせる</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -1850,12 +1854,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>うまい</t>
+          <t>わけです</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>好吃的；高明的</t>
+          <t>下结论</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1867,15 +1871,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>〜なんか</t>
+          <t>決して〜ない</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>...之类的（表轻视）</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>决不...</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>けっして〜ない</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -1884,19 +1892,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>強い</t>
+          <t>〜において</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>强壮的，强烈的</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>つよい</t>
-        </is>
-      </c>
+          <t>在…(方面，地点，时候)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -1905,12 +1909,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>あえて</t>
+          <t>お知らせ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>敢于，硬要</t>
+          <t>通知</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1918,16 +1922,16 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>まだ～ない</t>
+          <t>である</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>还没有…</t>
+          <t>是...（です的书面语）</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1939,12 +1943,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>いっこうに〜ない</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>一点也(不)...</t>
+          <t>所有的，一切的</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -1956,19 +1960,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>世話</t>
+          <t>〜だと</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>照顾，关照</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>せわ</t>
-        </is>
-      </c>
+          <t>…的话</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -1977,19 +1977,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>ミス</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>とはかぎらない</t>
-        </is>
-      </c>
+          <t>失误，错误</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -1998,40 +1994,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>自慢する</t>
+          <t>順番</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>自夸，炫耀</t>
+          <t>顺序；次序</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>じまんする</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>“我慢”忍耐</t>
-        </is>
-      </c>
+          <t>じゅんばん</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>まったく〜ない</t>
+          <t>任せる</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>完全(不)...</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>委托，托付</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>まかせる</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2040,15 +2036,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>いつか</t>
+          <t>〜を身につける</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>总有一天，某个时间</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>掌握...，学会...</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>〜をみにつける</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -2057,19 +2057,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>外れ者</t>
+          <t>〜とらえる</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>被排挤的人，不合群的人</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>はずれもの</t>
-        </is>
-      </c>
+          <t>视为...，理解为...</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -2078,17 +2074,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>気になる</t>
+          <t>的確に</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>在意，担心</t>
+          <t>准确地，恰当地</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>きになる</t>
+          <t>てきかくに</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2099,12 +2095,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>なぜなら</t>
+          <t>スムーズに</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>要说为什么…</t>
+          <t>顺利地</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2116,17 +2112,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>次が</t>
+          <t>話を広げる</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>下一个是...</t>
+          <t>展开话题</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>つぎが</t>
+          <t>はなしをひろげる</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2137,19 +2133,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>必死に</t>
+          <t>だけ〜ばいい</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>拼命地</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>ひっしに</t>
-        </is>
-      </c>
+          <t>只要...就行</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -2158,15 +2150,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>のに</t>
+          <t>〜に従って</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>为了…；转折</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>遵照...，随着...</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>〜にしたがって</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -2175,24 +2171,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>見つかる</t>
+          <t>〜が生じ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>被找到</t>
+          <t>发生...</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>みつかる</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>“みつける”寻找</t>
-        </is>
-      </c>
+          <t>〜がしょうじ</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2200,12 +2192,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>やめる</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>马上，立刻</t>
+          <t>停止，放弃</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2217,12 +2209,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>たとえ</t>
+          <t>たとえ〜でも</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>举例</t>
+          <t>即使...也...</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2234,15 +2226,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>たしかに</t>
+          <t>下記の</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>的确，确实</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>下述的，如下</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>かきの</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -2251,36 +2247,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>遅い</t>
+          <t>それ以上に</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>慢；迟；晚</t>
+          <t>在那之上，比那更...</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>おそい</t>
+          <t>それいじょうに</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>だから</t>
+          <t>〜に関する</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>所以，因此</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>关于...</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>〜にかんする</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr"/>
     </row>
   </sheetData>

--- a/READING/6_19_12.xlsx
+++ b/READING/6_19_12.xlsx
@@ -466,37 +466,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>立派な</t>
+          <t>あせって</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>出色的，宏伟的</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>りっぱな</t>
-        </is>
-      </c>
+          <t>着急地</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>〜は〜といわれる</t>
+          <t>ふくらむ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>...被称为...</t>
+          <t>膨胀；鼓起；扩大</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -504,37 +500,33 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>すべての</t>
+          <t>おのずとに</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>所有的</t>
+          <t>自然而然地</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>“あらゆる”全部，所有</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>どのように</t>
+          <t>～ております</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>以…方式</t>
+          <t>“ている”的自谦</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -542,37 +534,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>お手数ですが</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
+          <t>虽然很麻烦</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>とはかぎらない</t>
+          <t>おてすうですが</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>あせって</t>
+          <t>ようとして</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>着急地</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -580,113 +572,109 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ても仕方がない</t>
+          <t>〜により</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>...也没办法</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>てもしかたがない</t>
-        </is>
-      </c>
+          <t>通过…</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>どういう</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
+          <t>什么样的，怎样的</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>“ゆっくり”慢慢地</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>なさる</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“する”的尊敬语，上对下的语气</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>未必，不一定</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>とはかぎらない</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>何より</t>
+          <t>もち</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>比什么都...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>なにより</t>
-        </is>
-      </c>
+          <t>持ち</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>もち</t>
+          <t>出来る</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>持ち</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>能，会，可以</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>できる</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>おのずとに</t>
+          <t>ともいえます</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>自然而然地</t>
+          <t>也可以说是...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -694,79 +682,71 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>次第</t>
+          <t>〜も〜ば〜も</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>取决于</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>しだい</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>“N/Ｖ＋次第”一…就...</t>
-        </is>
-      </c>
+          <t>既...又...</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>だれだって</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ぶしょ</t>
-        </is>
-      </c>
+          <t>无论是谁都</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>あとは</t>
+          <t>何より</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>…之后</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>比什么都...</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>なにより</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>～ております</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>“ている”的自谦</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -774,41 +754,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>何かあったときに</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>发生什么事的时候</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>なにかあったときに</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>仔细地，慢慢地</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>“ゆっくり”慢慢地</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ようとして</t>
+          <t>あるいは</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>或者，也许</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>“〜または”或者</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -816,12 +800,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>どういう</t>
+          <t>どのように</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>什么样的，怎样的</t>
+          <t>以…方式</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -833,12 +817,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>〜は〜といわれる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>...被称为...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -846,16 +830,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>だろうか</t>
+          <t>といわれる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(1)反问，是…吗？(2)推测</t>
+          <t>被称为...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -863,57 +847,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>話し出し</t>
+          <t>ともに</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>开口说话，开场白</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>はなしだし</t>
-        </is>
-      </c>
+          <t>一起，同时</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>〜も〜ば〜も</t>
+          <t>目が行く</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>既...又...</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>注意到，目光投向</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>めがいく</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ふくらむ</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>膨胀；鼓起；扩大</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ぶしょ</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -922,76 +910,72 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ともに</t>
+          <t>納品</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>一起，同时</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>交货，送货</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>のうひん</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>あるいは</t>
+          <t>まったく〜ない</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>或者，也许</t>
+          <t>完全(不)...</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>“〜または”或者</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>出来る</t>
+          <t>まだ～ない</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>能，会，可以</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>できる</t>
-        </is>
-      </c>
+          <t>还没有…</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>任せる</t>
+          <t>妨げる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>委托，托付</t>
+          <t>妨碍，阻碍</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>まかせる</t>
+          <t>さまたげる</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1015,63 +999,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>遅い</t>
+          <t>思い込み</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>慢；迟；晚</t>
+          <t>深信，固执地认为</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>おそい</t>
+          <t>おもいこみ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>その一つ</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>其中之一</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>そのひとつ</t>
-        </is>
-      </c>
+          <t>相当，非常</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>的確に</t>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>准确地，恰当地</t>
+          <t>重复，反复</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>てきかくに</t>
+          <t>くりかえし</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1082,17 +1062,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>考え方がある</t>
+          <t>約束</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>有...样的想法/看法</t>
+          <t>约定，承诺</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>かんがえかたがある</t>
+          <t>やくそく</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1103,113 +1083,109 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>目が行く</t>
+          <t>〜に対して</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>注意到，目光投向</t>
+          <t>对于…</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>めがいく</t>
+          <t>〜にたいして</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>繰り返し</t>
+          <t>〜うち</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>重复，反复</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>くりかえし</t>
-        </is>
-      </c>
+          <t>在...期间；趁着</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>思い込み</t>
+          <t>だから</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>深信，固执地认为</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>おもいこみ</t>
-        </is>
-      </c>
+          <t>所以，因此</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ミス</t>
+          <t>何かあったときに</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>失误，错误</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>发生什么事的时候</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>なにかあったときに</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>〜に関する</t>
+          <t>すべての</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>关于...</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>〜にかんする</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>所有的</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>“あらゆる”全部，所有</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>お知らせ</t>
+          <t>あとは</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>通知</t>
+          <t>…之后</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1238,16 +1214,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜だと</t>
+          <t>だろうか</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>…的话</t>
+          <t>(1)反问，是…吗？(2)推测</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1255,126 +1231,146 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>ても仕方がない</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>...也没办法</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>てもしかたがない</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>である</t>
+          <t>話し出し</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>是...（です的书面语）</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>开口说话，开场白</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>はなしだし</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>〜を身につける</t>
+          <t>立派な</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>掌握...，学会...</t>
+          <t>出色的，宏伟的</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>〜をみにつける</t>
+          <t>りっぱな</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>順番</t>
+          <t>次第</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>顺序；次序</t>
+          <t>取决于</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>じゅんばん</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>しだい</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>“N/Ｖ＋次第”一…就...</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>〜において</t>
+          <t>回り道</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>在…(方面，地点，时候)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>绕道，走弯路</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>まわりみち</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>スムーズに</t>
+          <t>考え方がある</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>顺利地</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>有...样的想法/看法</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>かんがえかたがある</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>だから</t>
+          <t>なさる</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>所以，因此</t>
+          <t>“する”的尊敬语，上对下的语气</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1386,40 +1382,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>決して〜ない</t>
+          <t>必死に</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>决不...</t>
+          <t>拼命地</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>けっして〜ない</t>
+          <t>ひっしに</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>約束</t>
+          <t>いつか</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>约定，承诺</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>やくそく</t>
-        </is>
-      </c>
+          <t>总有一天，某个时间</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1428,15 +1420,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>だけ〜ばいい</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>只要...就行</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>未必，不一定</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>とはかぎらない</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1445,59 +1441,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>〜に従って</t>
+          <t>世話</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>遵照...，随着...</t>
+          <t>照顾，关照</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>せわ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>〜に対して</t>
+          <t>いっこうに〜ない</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>对于…</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>〜にたいして</t>
-        </is>
-      </c>
+          <t>一点也(不)...</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>納品</t>
+          <t>強い</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>交货，送货</t>
+          <t>强壮的，强烈的</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>のうひん</t>
+          <t>つよい</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1508,33 +1500,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>〜が生じ</t>
+          <t>あえて</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>发生...</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>〜がしょうじ</t>
-        </is>
-      </c>
+          <t>敢于，硬要</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>〜により</t>
+          <t>〜なんか</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>通过…</t>
+          <t>...之类的（表轻视）</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1546,12 +1534,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>〜とらえる</t>
+          <t>うまい</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>视为...，理解为...</t>
+          <t>好吃的；高明的</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1563,20 +1551,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>合わせる</t>
+          <t>自慢する</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>配合；合计</t>
+          <t>自夸，炫耀</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>あわせる</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>じまんする</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>“我慢”忍耐</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1584,53 +1576,61 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>たとえ〜でも</t>
+          <t>一方的に</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>即使...也...</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>单方面地</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>いっぽうてきに</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>お手数ですが</t>
+          <t>外れ者</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>虽然很麻烦</t>
+          <t>被排挤的人，不合群的人</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>おてすうですが</t>
+          <t>はずれもの</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>だれだって</t>
+          <t>気味</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>无论是谁都</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>有点...，感觉...</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>きみ</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -1639,17 +1639,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>下記の</t>
+          <t>気になる</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>下述的，如下</t>
+          <t>在意，担心</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>かきの</t>
+          <t>きになる</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>いつか</t>
+          <t>なぜなら</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>总有一天，某个时间</t>
+          <t>要说为什么…</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>それ以上に</t>
+          <t>次が</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>在那之上，比那更...</t>
+          <t>下一个是...</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>それいじょうに</t>
+          <t>つぎが</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1698,33 +1698,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>話を広げる</t>
+          <t>すぐに</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>展开话题</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>はなしをひろげる</t>
-        </is>
-      </c>
+          <t>马上，立刻</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>のに</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>相当，非常</t>
+          <t>为了…；转折</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1736,16 +1732,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>わけです</t>
+          <t>見つかる</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>下结论</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+          <t>被找到</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>みつかる</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>“みつける”寻找</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1753,19 +1757,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>必死に</t>
+          <t>たとえ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>拼命地</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>ひっしに</t>
-        </is>
-      </c>
+          <t>举例</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>うまい</t>
+          <t>たしかに</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>好吃的；高明的</t>
+          <t>的确，确实</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1791,15 +1791,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>〜なんか</t>
+          <t>遅い</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>...之类的（表轻视）</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>慢；迟；晚</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>おそい</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -1808,17 +1812,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>強い</t>
+          <t>その一つ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>强壮的，强烈的</t>
+          <t>其中之一</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>つよい</t>
+          <t>そのひとつ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -1829,29 +1833,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>あえて</t>
+          <t>合わせる</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>敢于，硬要</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>配合；合计</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>あわせる</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ともいえます</t>
+          <t>わけです</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>也可以说是...</t>
+          <t>下结论</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1859,19 +1867,23 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>といわれる</t>
+          <t>決して〜ない</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>被称为...</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>决不...</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>けっして〜ない</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -1880,19 +1892,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>世話</t>
+          <t>〜において</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>照顾，关照</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>せわ</t>
-        </is>
-      </c>
+          <t>在…(方面，地点，时候)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -1901,24 +1909,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>自慢する</t>
+          <t>お知らせ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>自夸，炫耀</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>じまんする</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>“我慢”忍耐</t>
-        </is>
-      </c>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1926,19 +1926,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>外れ者</t>
+          <t>である</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>被排挤的人，不合群的人</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>はずれもの</t>
-        </is>
-      </c>
+          <t>是...（です的书面语）</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -1947,19 +1943,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>気になる</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>在意，担心</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>きになる</t>
-        </is>
-      </c>
+          <t>所有的，一切的</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -1968,40 +1960,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>次が</t>
+          <t>〜だと</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>下一个是...</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>つぎが</t>
-        </is>
-      </c>
+          <t>…的话</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>回り道</t>
+          <t>ミス</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>绕道，走弯路</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>まわりみち</t>
-        </is>
-      </c>
+          <t>失误，错误</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -2010,24 +1994,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>見つかる</t>
+          <t>順番</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>被找到</t>
+          <t>顺序；次序</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>みつかる</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>“みつける”寻找</t>
-        </is>
-      </c>
+          <t>じゅんばん</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2035,15 +2015,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>任せる</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>马上，立刻</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>委托，托付</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>まかせる</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2052,15 +2036,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>たとえ</t>
+          <t>〜を身につける</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>举例</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>掌握...，学会...</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>〜をみにつける</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -2069,12 +2057,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>たしかに</t>
+          <t>〜とらえる</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>的确，确实</t>
+          <t>视为...，理解为...</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2086,17 +2074,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>気味</t>
+          <t>的確に</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>有点...，感觉...</t>
+          <t>准确地，恰当地</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>きみ</t>
+          <t>てきかくに</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2107,19 +2095,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>一方的に</t>
+          <t>スムーズに</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>单方面地</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>いっぽうてきに</t>
-        </is>
-      </c>
+          <t>顺利地</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -2128,15 +2112,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>のに</t>
+          <t>話を広げる</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>为了…；转折</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>展开话题</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>はなしをひろげる</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -2145,12 +2133,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>なぜなら</t>
+          <t>だけ〜ばいい</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>要说为什么…</t>
+          <t>只要...就行</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2162,15 +2150,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>まったく〜ない</t>
+          <t>〜に従って</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>完全(不)...</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>遵照...，随着...</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>〜にしたがって</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -2179,15 +2171,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>やめる</t>
+          <t>〜が生じ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>停止，放弃</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>发生...</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>〜がしょうじ</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -2196,19 +2192,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>やめる</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>とはかぎらない</t>
-        </is>
-      </c>
+          <t>停止，放弃</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -2217,12 +2209,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>いっこうに〜ない</t>
+          <t>たとえ〜でも</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>一点也(不)...</t>
+          <t>即使...也...</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2234,15 +2226,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>まだ～ない</t>
+          <t>下記の</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>还没有…</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>下述的，如下</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>かきの</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -2251,36 +2247,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>妨げる</t>
+          <t>それ以上に</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>妨碍，阻碍</t>
+          <t>在那之上，比那更...</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>さまたげる</t>
+          <t>それいじょうに</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>〜うち</t>
+          <t>〜に関する</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>在...期间；趁着</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>关于...</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>〜にかんする</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr"/>
     </row>
   </sheetData>

--- a/READING/6_19_12.xlsx
+++ b/READING/6_19_12.xlsx
@@ -466,33 +466,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>あせって</t>
+          <t>立派な</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>着急地</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>出色的，宏伟的</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>りっぱな</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ふくらむ</t>
+          <t>〜は〜といわれる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>膨胀；鼓起；扩大</t>
+          <t>...被称为...</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -500,33 +504,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>おのずとに</t>
+          <t>すべての</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>自然而然地</t>
+          <t>所有的</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>“あらゆる”全部，所有</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>～ております</t>
+          <t>どのように</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“ている”的自谦</t>
+          <t>以…方式</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -534,37 +542,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>お手数ですが</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>虽然很麻烦</t>
+          <t>未必，不一定</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>おてすうですが</t>
+          <t>とはかぎらない</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ようとして</t>
+          <t>あせって</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>着急地</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -572,109 +580,113 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>〜により</t>
+          <t>ても仕方がない</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>通过…</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>...也没办法</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>てもしかたがない</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>どういう</t>
+          <t>じっくり</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>什么样的，怎样的</t>
+          <t>仔细地，慢慢地</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>“ゆっくり”慢慢地</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>なさる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>とはかぎらない</t>
-        </is>
-      </c>
+          <t>“する”的尊敬语，上对下的语气</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>もち</t>
+          <t>何より</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>持ち</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>比什么都...</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>なにより</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>出来る</t>
+          <t>もち</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>能，会，可以</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>できる</t>
-        </is>
-      </c>
+          <t>持ち</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ともいえます</t>
+          <t>おのずとに</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>也可以说是...</t>
+          <t>自然而然地</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -682,71 +694,79 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜も〜ば〜も</t>
+          <t>次第</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>既...又...</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>取决于</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>しだい</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>“N/Ｖ＋次第”一…就...</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>だれだって</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>无论是谁都</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ぶしょ</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>何より</t>
+          <t>あとは</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>比什么都...</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>なにより</t>
-        </is>
-      </c>
+          <t>…之后</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>～ております</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>想要/试图做...</t>
+          <t>“ている”的自谦</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -754,45 +774,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>じっくり</t>
+          <t>何かあったときに</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>仔细地，慢慢地</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>“ゆっくり”慢慢地</t>
-        </is>
-      </c>
+          <t>发生什么事的时候</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>なにかあったときに</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>あるいは</t>
+          <t>ようとして</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>或者，也许</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>“〜または”或者</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -800,12 +816,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>どのように</t>
+          <t>どういう</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>以…方式</t>
+          <t>什么样的，怎样的</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -817,12 +833,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜は〜といわれる</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>...被称为...</t>
+          <t>想要/试图做...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -830,16 +846,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>といわれる</t>
+          <t>だろうか</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>被称为...</t>
+          <t>(1)反问，是…吗？(2)推测</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -847,61 +863,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ともに</t>
+          <t>話し出し</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>一起，同时</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>开口说话，开场白</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>はなしだし</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>目が行く</t>
+          <t>〜も〜ば〜も</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>注意到，目光投向</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>めがいく</t>
-        </is>
-      </c>
+          <t>既...又...</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>ふくらむ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ぶしょ</t>
-        </is>
-      </c>
+          <t>膨胀；鼓起；扩大</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -910,72 +922,76 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>納品</t>
+          <t>ともに</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>交货，送货</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>のうひん</t>
-        </is>
-      </c>
+          <t>一起，同时</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>まったく〜ない</t>
+          <t>あるいは</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>完全(不)...</t>
+          <t>或者，也许</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>“〜または”或者</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>まだ～ない</t>
+          <t>出来る</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>还没有…</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>能，会，可以</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>できる</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>妨げる</t>
+          <t>任せる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>妨碍，阻碍</t>
+          <t>委托，托付</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>さまたげる</t>
+          <t>まかせる</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -999,59 +1015,63 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>思い込み</t>
+          <t>遅い</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>深信，固执地认为</t>
+          <t>慢；迟；晚</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>おもいこみ</t>
+          <t>おそい</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>その一つ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>相当，非常</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>其中之一</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>そのひとつ</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>繰り返し</t>
+          <t>的確に</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>重复，反复</t>
+          <t>准确地，恰当地</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>くりかえし</t>
+          <t>てきかくに</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1062,17 +1082,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>約束</t>
+          <t>考え方がある</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>约定，承诺</t>
+          <t>有...样的想法/看法</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>やくそく</t>
+          <t>かんがえかたがある</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1083,109 +1103,113 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>〜に対して</t>
+          <t>目が行く</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>对于…</t>
+          <t>注意到，目光投向</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>〜にたいして</t>
+          <t>めがいく</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>〜うち</t>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>在...期间；趁着</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>重复，反复</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>くりかえし</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>だから</t>
+          <t>思い込み</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>所以，因此</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>深信，固执地认为</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>おもいこみ</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>何かあったときに</t>
+          <t>ミス</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>发生什么事的时候</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>なにかあったときに</t>
-        </is>
-      </c>
+          <t>失误，错误</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>すべての</t>
+          <t>〜に関する</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>所有的</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>“あらゆる”全部，所有</t>
-        </is>
-      </c>
+          <t>关于...</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>〜にかんする</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>あとは</t>
+          <t>お知らせ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>…之后</t>
+          <t>通知</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1214,16 +1238,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>だろうか</t>
+          <t>〜だと</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(1)反问，是…吗？(2)推测</t>
+          <t>…的话</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1231,146 +1255,126 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ても仕方がない</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>...也没办法</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>てもしかたがない</t>
-        </is>
-      </c>
+          <t>所有的，一切的</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>話し出し</t>
+          <t>である</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>开口说话，开场白</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>はなしだし</t>
-        </is>
-      </c>
+          <t>是...（です的书面语）</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>立派な</t>
+          <t>〜を身につける</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>出色的，宏伟的</t>
+          <t>掌握...，学会...</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>りっぱな</t>
+          <t>〜をみにつける</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>次第</t>
+          <t>順番</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>取决于</t>
+          <t>顺序；次序</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>しだい</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>“N/Ｖ＋次第”一…就...</t>
-        </is>
-      </c>
+          <t>じゅんばん</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>回り道</t>
+          <t>〜において</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>绕道，走弯路</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>まわりみち</t>
-        </is>
-      </c>
+          <t>在…(方面，地点，时候)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>考え方がある</t>
+          <t>スムーズに</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>有...样的想法/看法</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>かんがえかたがある</t>
-        </is>
-      </c>
+          <t>顺利地</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>なさる</t>
+          <t>だから</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>“する”的尊敬语，上对下的语气</t>
+          <t>所以，因此</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1382,36 +1386,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>必死に</t>
+          <t>決して〜ない</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>拼命地</t>
+          <t>决不...</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ひっしに</t>
+          <t>けっして〜ない</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>いつか</t>
+          <t>約束</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>总有一天，某个时间</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>约定，承诺</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>やくそく</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1420,19 +1428,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>とは限らない</t>
+          <t>だけ〜ばいい</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>未必，不一定</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>とはかぎらない</t>
-        </is>
-      </c>
+          <t>只要...就行</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1441,55 +1445,59 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>世話</t>
+          <t>〜に従って</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>照顾，关照</t>
+          <t>遵照...，随着...</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>せわ</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>いっこうに〜ない</t>
+          <t>〜に対して</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>一点也(不)...</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>对于…</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>〜にたいして</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>強い</t>
+          <t>納品</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>强壮的，强烈的</t>
+          <t>交货，送货</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>つよい</t>
+          <t>のうひん</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1500,29 +1508,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>あえて</t>
+          <t>〜が生じ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>敢于，硬要</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>发生...</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>〜がしょうじ</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>〜なんか</t>
+          <t>〜により</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>...之类的（表轻视）</t>
+          <t>通过…</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1534,12 +1546,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>うまい</t>
+          <t>〜とらえる</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>好吃的；高明的</t>
+          <t>视为...，理解为...</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1551,24 +1563,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>自慢する</t>
+          <t>合わせる</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>自夸，炫耀</t>
+          <t>配合；合计</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>じまんする</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>“我慢”忍耐</t>
-        </is>
-      </c>
+          <t>あわせる</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1576,61 +1584,53 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>一方的に</t>
+          <t>たとえ〜でも</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>单方面地</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>いっぽうてきに</t>
-        </is>
-      </c>
+          <t>即使...也...</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>外れ者</t>
+          <t>お手数ですが</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>被排挤的人，不合群的人</t>
+          <t>虽然很麻烦</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>はずれもの</t>
+          <t>おてすうですが</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>気味</t>
+          <t>だれだって</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>有点...，感觉...</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>きみ</t>
-        </is>
-      </c>
+          <t>无论是谁都</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -1639,17 +1639,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>気になる</t>
+          <t>下記の</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>在意，担心</t>
+          <t>下述的，如下</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>きになる</t>
+          <t>かきの</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>なぜなら</t>
+          <t>いつか</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>要说为什么…</t>
+          <t>总有一天，某个时间</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>次が</t>
+          <t>それ以上に</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>下一个是...</t>
+          <t>在那之上，比那更...</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>つぎが</t>
+          <t>それいじょうに</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1698,29 +1698,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>話を広げる</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>马上，立刻</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>展开话题</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>はなしをひろげる</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>のに</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>为了…；转折</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1732,24 +1736,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>見つかる</t>
+          <t>わけです</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>被找到</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>みつかる</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>“みつける”寻找</t>
-        </is>
-      </c>
+          <t>下结论</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1757,15 +1753,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>たとえ</t>
+          <t>必死に</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>举例</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>拼命地</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ひっしに</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>たしかに</t>
+          <t>うまい</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>的确，确实</t>
+          <t>好吃的；高明的</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1791,19 +1791,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>遅い</t>
+          <t>〜なんか</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>慢；迟；晚</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>おそい</t>
-        </is>
-      </c>
+          <t>...之类的（表轻视）</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -1812,17 +1808,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>その一つ</t>
+          <t>強い</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>其中之一</t>
+          <t>强壮的，强烈的</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>そのひとつ</t>
+          <t>つよい</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -1833,33 +1829,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>合わせる</t>
+          <t>あえて</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>配合；合计</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>あわせる</t>
-        </is>
-      </c>
+          <t>敢于，硬要</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>わけです</t>
+          <t>ともいえます</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>下结论</t>
+          <t>也可以说是...</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1867,23 +1859,19 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>決して〜ない</t>
+          <t>といわれる</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>决不...</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>けっして〜ない</t>
-        </is>
-      </c>
+          <t>被称为...</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -1892,15 +1880,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>〜において</t>
+          <t>世話</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>在…(方面，地点，时候)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>照顾，关照</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>せわ</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -1909,16 +1901,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>お知らせ</t>
+          <t>自慢する</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+          <t>自夸，炫耀</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>じまんする</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>“我慢”忍耐</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1926,15 +1926,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>である</t>
+          <t>外れ者</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>是...（です的书面语）</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>被排挤的人，不合群的人</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>はずれもの</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -1943,15 +1947,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>気になる</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>在意，担心</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>きになる</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -1960,32 +1968,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>〜だと</t>
+          <t>次が</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>…的话</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>下一个是...</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>つぎが</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ミス</t>
+          <t>回り道</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>失误，错误</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>绕道，走弯路</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>まわりみち</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -1994,20 +2010,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>順番</t>
+          <t>見つかる</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>顺序；次序</t>
+          <t>被找到</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>じゅんばん</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>みつかる</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>“みつける”寻找</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2015,19 +2035,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>任せる</t>
+          <t>すぐに</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>委托，托付</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>まかせる</t>
-        </is>
-      </c>
+          <t>马上，立刻</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2036,19 +2052,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>〜を身につける</t>
+          <t>たとえ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>掌握...，学会...</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>〜をみにつける</t>
-        </is>
-      </c>
+          <t>举例</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -2057,12 +2069,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>〜とらえる</t>
+          <t>たしかに</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>视为...，理解为...</t>
+          <t>的确，确实</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2074,17 +2086,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>的確に</t>
+          <t>気味</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>准确地，恰当地</t>
+          <t>有点...，感觉...</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>てきかくに</t>
+          <t>きみ</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2095,15 +2107,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>スムーズに</t>
+          <t>一方的に</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>顺利地</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>单方面地</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>いっぽうてきに</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -2112,19 +2128,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>話を広げる</t>
+          <t>のに</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>展开话题</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>はなしをひろげる</t>
-        </is>
-      </c>
+          <t>为了…；转折</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -2133,12 +2145,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>だけ〜ばいい</t>
+          <t>なぜなら</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>只要...就行</t>
+          <t>要说为什么…</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2150,19 +2162,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>〜に従って</t>
+          <t>まったく〜ない</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>遵照...，随着...</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>〜にしたがって</t>
-        </is>
-      </c>
+          <t>完全(不)...</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -2171,19 +2179,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>〜が生じ</t>
+          <t>やめる</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>发生...</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>〜がしょうじ</t>
-        </is>
-      </c>
+          <t>停止，放弃</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -2192,15 +2196,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>やめる</t>
+          <t>とは限らない</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>停止，放弃</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>未必，不一定</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>とはかぎらない</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -2209,12 +2217,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>たとえ〜でも</t>
+          <t>いっこうに〜ない</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>即使...也...</t>
+          <t>一点也(不)...</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2226,19 +2234,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>下記の</t>
+          <t>まだ～ない</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>下述的，如下</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>かきの</t>
-        </is>
-      </c>
+          <t>还没有…</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -2247,40 +2251,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>それ以上に</t>
+          <t>妨げる</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>在那之上，比那更...</t>
+          <t>妨碍，阻碍</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>それいじょうに</t>
+          <t>さまたげる</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>〜に関する</t>
+          <t>〜うち</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>关于...</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>〜にかんする</t>
-        </is>
-      </c>
+          <t>在...期间；趁着</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
     </row>
   </sheetData>

--- a/READING/6_19_12.xlsx
+++ b/READING/6_19_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E04A2-EC77-421C-9225-E6E935740229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F112AC-24E2-439B-AD40-57FACC6FB445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10275" yWindow="690" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15405" yWindow="1005" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="245">
   <si>
     <t>Fre</t>
   </si>
@@ -220,9 +220,6 @@
   </si>
   <si>
     <t>所有的</t>
-  </si>
-  <si>
-    <t>“あらゆる”全部，所有</t>
   </si>
   <si>
     <t>〜うち</t>
@@ -757,6 +754,18 @@
   </si>
   <si>
     <t>次第</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>“あらゆる”全部，所有</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あらゆる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部，所有</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1128,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1199,7 +1208,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
@@ -1207,7 +1216,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -1240,7 +1249,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -1254,7 +1263,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
@@ -1268,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -1279,7 +1288,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -1290,7 +1299,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
@@ -1498,13 +1507,10 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>243</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" t="s">
-        <v>66</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
@@ -1512,10 +1518,13 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
@@ -1523,13 +1532,10 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
@@ -1537,10 +1543,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>69</v>
+      </c>
+      <c r="D33" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
@@ -1548,13 +1557,10 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1562,13 +1568,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1576,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1590,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
@@ -1604,10 +1610,13 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
@@ -1615,13 +1624,10 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1629,13 +1635,13 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1643,13 +1649,13 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -1657,10 +1663,13 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="D42" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -1668,13 +1677,10 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D43" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -1682,13 +1688,13 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1696,10 +1702,13 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>102</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1707,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1718,10 +1727,10 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1729,13 +1738,10 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
@@ -1743,30 +1749,27 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
@@ -1774,13 +1777,16 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>118</v>
+      </c>
+      <c r="E51" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
@@ -1788,10 +1794,13 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
@@ -1799,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
@@ -1810,10 +1819,10 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
@@ -1821,13 +1830,10 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
@@ -1835,13 +1841,13 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
@@ -1849,10 +1855,13 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="D57" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
@@ -1860,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
@@ -1871,13 +1880,10 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
-      </c>
-      <c r="D59" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
@@ -1885,13 +1891,13 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C60" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
@@ -1899,16 +1905,13 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
-      </c>
-      <c r="E61" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
@@ -1916,13 +1919,16 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>144</v>
+      </c>
+      <c r="E62" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
@@ -1930,10 +1936,13 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="D63" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
@@ -1941,13 +1950,10 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C64" t="s">
-        <v>153</v>
-      </c>
-      <c r="D64" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
@@ -1955,10 +1961,13 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="D65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
@@ -1966,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
@@ -1977,13 +1986,10 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C67" t="s">
-        <v>160</v>
-      </c>
-      <c r="D67" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
@@ -1991,13 +1997,13 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D68" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
@@ -2005,13 +2011,13 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
@@ -2019,10 +2025,13 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>169</v>
+        <v>165</v>
+      </c>
+      <c r="D70" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
@@ -2030,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
@@ -2041,13 +2050,10 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
@@ -2055,10 +2061,13 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>172</v>
+      </c>
+      <c r="E73" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
@@ -2066,13 +2075,10 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C74" t="s">
-        <v>178</v>
-      </c>
-      <c r="D74" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
@@ -2080,10 +2086,13 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C75" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="D75" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
@@ -2091,13 +2100,10 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C76" t="s">
-        <v>183</v>
-      </c>
-      <c r="D76" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
@@ -2105,10 +2111,13 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C77" t="s">
-        <v>186</v>
+        <v>182</v>
+      </c>
+      <c r="D77" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.15">
@@ -2116,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C78" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
@@ -2127,13 +2136,10 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
-      </c>
-      <c r="D79" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
@@ -2141,10 +2147,13 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C80" t="s">
-        <v>193</v>
+        <v>189</v>
+      </c>
+      <c r="D80" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
@@ -2152,13 +2161,10 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C81" t="s">
-        <v>195</v>
-      </c>
-      <c r="D81" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
@@ -2166,10 +2172,13 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="D82" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
@@ -2177,13 +2186,10 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C83" t="s">
-        <v>200</v>
-      </c>
-      <c r="D83" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
@@ -2191,10 +2197,13 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C84" t="s">
-        <v>203</v>
+        <v>199</v>
+      </c>
+      <c r="D84" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
@@ -2202,13 +2211,10 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
-      </c>
-      <c r="D85" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
@@ -2216,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C86" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D86" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
@@ -2230,10 +2236,13 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C87" t="s">
-        <v>211</v>
+        <v>207</v>
+      </c>
+      <c r="D87" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
@@ -2241,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C88" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
@@ -2252,13 +2261,10 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C89" t="s">
-        <v>215</v>
-      </c>
-      <c r="D89" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
@@ -2266,13 +2272,13 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C90" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D90" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
@@ -2280,13 +2286,13 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C91" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D91" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
@@ -2294,10 +2300,13 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C92" t="s">
-        <v>224</v>
+        <v>220</v>
+      </c>
+      <c r="D92" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
@@ -2305,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C93" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
@@ -2316,13 +2325,10 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>228</v>
-      </c>
-      <c r="D94" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
@@ -2330,13 +2336,13 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D95" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
@@ -2344,13 +2350,27 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C96" t="s">
+        <v>230</v>
+      </c>
+      <c r="D96" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A97">
+        <v>0</v>
+      </c>
+      <c r="B97" t="s">
+        <v>232</v>
+      </c>
+      <c r="C97" t="s">
         <v>233</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D97" t="s">
         <v>234</v>
-      </c>
-      <c r="D96" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>
